--- a/1 Resources/SleepyVehicles.xlsx
+++ b/1 Resources/SleepyVehicles.xlsx
@@ -9,13 +9,14 @@
   <sheets>
     <sheet name="Vehicles" sheetId="1" r:id="rId1"/>
     <sheet name="Weights" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="72">
   <si>
     <t>Type</t>
   </si>
@@ -198,6 +199,39 @@
   </si>
   <si>
     <t>SEARCH=0.50,INJURED=0.25</t>
+  </si>
+  <si>
+    <t>AU ACT Rosenbauer Hybrid-Electric</t>
+  </si>
+  <si>
+    <t>Bonuses</t>
+  </si>
+  <si>
+    <t>SEARCH,</t>
+  </si>
+  <si>
+    <t>STUN</t>
+  </si>
+  <si>
+    <t>DYING</t>
+  </si>
+  <si>
+    <t>TALL</t>
+  </si>
+  <si>
+    <t>TECH</t>
+  </si>
+  <si>
+    <t>FIRE</t>
+  </si>
+  <si>
+    <t>INJURED</t>
+  </si>
+  <si>
+    <t>FIRE=0.5,TECH=0.25,INJURED=0.15</t>
+  </si>
+  <si>
+    <t>AU SA Tatra Force T815-7</t>
   </si>
 </sst>
 </file>
@@ -207,7 +241,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,8 +262,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -254,6 +296,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -267,7 +315,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -336,6 +384,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -741,7 +794,7 @@
   <cols>
     <col min="1" max="1" width="1.28515625" customWidth="1"/>
     <col min="2" max="2" width="9.5703125" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="3" max="3" width="34.85546875" customWidth="1"/>
     <col min="4" max="5" width="12.5703125" customWidth="1"/>
     <col min="6" max="6" width="9.85546875" customWidth="1"/>
     <col min="7" max="7" width="10.5703125" customWidth="1"/>
@@ -766,7 +819,7 @@
       </c>
       <c r="C1">
         <f>COUNTA(Table1[Name])-6</f>
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="2:20">
@@ -2180,56 +2233,128 @@
       </c>
     </row>
     <row r="26" spans="2:20">
-      <c r="D26" s="12"/>
+      <c r="B26" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="12">
+        <v>180000</v>
+      </c>
       <c r="E26" s="33">
         <f>Table1[[#This Row],[AUD Cost]]/1.75</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="27" t="e">
-        <f>(Table1[[#This Row],[XML Cost]]/((Table1[[#This Row],[Speed]]*Weights!$C$2)+(Table1[[#This Row],[Armour]]*Weights!$C$3)+(Table1[[#This Row],[Water]]*Weights!$C$4)+(Table1[[#This Row],[Acceleration]]*Weights!$C$5)+(Table1[[#This Row],[Offroad Mod]]*Weights!$C$6)+(Table1[[#This Row],[T. Seats]]*Weights!$C$8)+(Table1[[#This Row],[P. Seats]]*Weights!$C$9)+(Table1[[#This Row],[Traffic Mod]]*Weights!$C$7))/100)</f>
-        <v>#DIV/0!</v>
+        <v>102857.14285714286</v>
+      </c>
+      <c r="F26" s="27">
+        <f>(Table1[[#This Row],[XML Cost]]/((Table1[[#This Row],[Speed]]*Weights!$C$2)+(Table1[[#This Row],[Armour]]*Weights!$C$3)+(Table1[[#This Row],[Water]]*Weights!$C$4)+(Table1[[#This Row],[Acceleration]]*Weights!$C$5)+(Table1[[#This Row],[Offroad Mod]]*Weights!$C$6)+(Table1[[#This Row],[T. Seats]]*Weights!$C$8)+(Table1[[#This Row],[P. Seats]]*Weights!$C$9)+(Table1[[#This Row],[Traffic Mod]]*Weights!$C$7))/100)</f>
+        <v>1.9047619047619049</v>
       </c>
       <c r="G26" s="32">
         <f>Table1[[#This Row],[AUD Cost]]/100</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="1"/>
-      <c r="T26" s="1"/>
+        <v>1800</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2">
+        <v>15</v>
+      </c>
+      <c r="K26">
+        <v>120</v>
+      </c>
+      <c r="L26" s="2">
+        <v>3</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N26" s="2">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>0</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26" s="36" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="27" spans="2:20">
-      <c r="D27" s="12"/>
+      <c r="B27" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" s="12">
+        <v>150000</v>
+      </c>
       <c r="E27" s="33">
         <f>Table1[[#This Row],[AUD Cost]]/1.75</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="27" t="e">
-        <f>(Table1[[#This Row],[XML Cost]]/((Table1[[#This Row],[Speed]]*Weights!$C$2)+(Table1[[#This Row],[Armour]]*Weights!$C$3)+(Table1[[#This Row],[Water]]*Weights!$C$4)+(Table1[[#This Row],[Acceleration]]*Weights!$C$5)+(Table1[[#This Row],[Offroad Mod]]*Weights!$C$6)+(Table1[[#This Row],[T. Seats]]*Weights!$C$8)+(Table1[[#This Row],[P. Seats]]*Weights!$C$9)+(Table1[[#This Row],[Traffic Mod]]*Weights!$C$7))/100)</f>
-        <v>#DIV/0!</v>
+        <v>85714.28571428571</v>
+      </c>
+      <c r="F27" s="27">
+        <f>(Table1[[#This Row],[XML Cost]]/((Table1[[#This Row],[Speed]]*Weights!$C$2)+(Table1[[#This Row],[Armour]]*Weights!$C$3)+(Table1[[#This Row],[Water]]*Weights!$C$4)+(Table1[[#This Row],[Acceleration]]*Weights!$C$5)+(Table1[[#This Row],[Offroad Mod]]*Weights!$C$6)+(Table1[[#This Row],[T. Seats]]*Weights!$C$8)+(Table1[[#This Row],[P. Seats]]*Weights!$C$9)+(Table1[[#This Row],[Traffic Mod]]*Weights!$C$7))/100)</f>
+        <v>2.0855057351407713</v>
       </c>
       <c r="G27" s="32">
         <f>Table1[[#This Row],[AUD Cost]]/100</f>
-        <v>0</v>
-      </c>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="2"/>
-      <c r="R27" s="1"/>
-      <c r="T27" s="1"/>
+        <v>1500</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2">
+        <v>6</v>
+      </c>
+      <c r="K27">
+        <v>100</v>
+      </c>
+      <c r="L27" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N27" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="O27" s="2">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>0</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27" s="36" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="28" spans="2:20">
       <c r="D28" s="12"/>
@@ -2631,4 +2756,54 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B2:B9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2" spans="2:2">
+      <c r="B2" s="37" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>